--- a/output/topology_excel/13829.xlsx
+++ b/output/topology_excel/13829.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="F11" t="n">
-        <v>118</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -707,29 +707,29 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>117</v>
+      </c>
+      <c r="F13" t="n">
         <v>11</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>175</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>358</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>358</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,15 +916,15 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
         <v>10</v>
@@ -938,15 +938,15 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
         <v>12</v>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,15 +1004,15 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
         <v>13</v>
@@ -1026,10 +1026,76 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>117</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>111</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/13829.xlsx
+++ b/output/topology_excel/13829.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
